--- a/Gerbers/V2/BOM_V2.xlsx
+++ b/Gerbers/V2/BOM_V2.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_V2_PCB2_2026-08-02" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_V2_PCB2_2026-09-16" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="108">
   <si>
     <t>No.</t>
   </si>
@@ -70,6 +70,18 @@
     <t>2</t>
   </si>
   <si>
+    <t>Test-Point</t>
+  </si>
+  <si>
+    <t>3.3V,D0,EN,GND</t>
+  </si>
+  <si>
+    <t>Test-Point-0.5mm</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>ZX-SH1.0-2PWT</t>
   </si>
   <si>
@@ -85,7 +97,7 @@
     <t>C7430444</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>100nF</t>
@@ -106,18 +118,6 @@
     <t>C1525</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Test-Point</t>
-  </si>
-  <si>
-    <t>D0,GND</t>
-  </si>
-  <si>
-    <t>Test-Point-0.5mm</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -154,6 +154,24 @@
     <t>7</t>
   </si>
   <si>
+    <t>CBM100505U201T</t>
+  </si>
+  <si>
+    <t>FB1</t>
+  </si>
+  <si>
+    <t>L0402</t>
+  </si>
+  <si>
+    <t>FH(风华)</t>
+  </si>
+  <si>
+    <t>C394402</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>SMD-16-P2.54</t>
   </si>
   <si>
@@ -166,7 +184,7 @@
     <t>C9900001406</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>2.54-1*20P母</t>
@@ -184,7 +202,7 @@
     <t>C50984</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>22Ω</t>
@@ -205,7 +223,28 @@
     <t>C107701</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
+  </si>
+  <si>
+    <t>2kΩ</t>
+  </si>
+  <si>
+    <t>R7,R8</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>0402WGF2001TCE</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>C4109</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>SK6812MINI</t>
@@ -226,7 +265,7 @@
     <t>C2886570</t>
   </si>
   <si>
-    <t>11</t>
+    <t>13</t>
   </si>
   <si>
     <t>220Ω</t>
@@ -244,7 +283,7 @@
     <t>C1731723</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>MHT194UGBCT</t>
@@ -262,7 +301,7 @@
     <t>C2764896</t>
   </si>
   <si>
-    <t>13</t>
+    <t>15</t>
   </si>
   <si>
     <t>DS3231MZ+</t>
@@ -280,7 +319,7 @@
     <t>C722467</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>XDWF-0910-05P</t>
@@ -672,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="20" customWidth="1"/>
@@ -747,7 +786,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
@@ -762,45 +801,45 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -808,34 +847,34 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" t="s">
         <v>32</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H5" t="s">
         <v>33</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" t="s">
-        <v>14</v>
-      </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -893,7 +932,7 @@
         <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
         <v>45</v>
@@ -925,10 +964,10 @@
         <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -936,28 +975,28 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
         <v>53</v>
       </c>
-      <c r="E9" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" t="s">
-        <v>52</v>
-      </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="I9" t="s">
         <v>56</v>
@@ -971,7 +1010,7 @@
         <v>57</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
         <v>58</v>
@@ -983,16 +1022,16 @@
         <v>60</v>
       </c>
       <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
         <v>58</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>61</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>62</v>
-      </c>
-      <c r="I10" t="s">
-        <v>63</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -1000,31 +1039,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
         <v>64</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>65</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>66</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" t="s">
         <v>67</v>
       </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>68</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>69</v>
-      </c>
-      <c r="I11" t="s">
-        <v>70</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -1032,28 +1071,28 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
         <v>71</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>72</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>73</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" t="s">
         <v>74</v>
       </c>
-      <c r="F12" t="s">
-        <v>72</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>75</v>
-      </c>
-      <c r="H12" t="s">
-        <v>62</v>
       </c>
       <c r="I12" t="s">
         <v>76</v>
@@ -1082,13 +1121,13 @@
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
@@ -1096,31 +1135,31 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
         <v>85</v>
       </c>
-      <c r="E14" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
       <c r="G14" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="I14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
@@ -1128,38 +1167,102 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
         <v>91</v>
       </c>
-      <c r="E15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" t="s">
-        <v>90</v>
-      </c>
       <c r="H15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" t="s">
+        <v>106</v>
+      </c>
+      <c r="I17" t="s">
+        <v>107</v>
+      </c>
+      <c r="J17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>14</v>
       </c>
     </row>
